--- a/data/trans_dic/P15B_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,94; 28,78</t>
+          <t>5,62; 29,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 16,13</t>
+          <t>3,06; 16,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,68</t>
+          <t>0,0; 11,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,41</t>
+          <t>0,0; 76,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,56</t>
+          <t>0,0; 15,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,07</t>
+          <t>0,0; 32,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,16</t>
+          <t>0,0; 51,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 24,11</t>
+          <t>4,36; 24,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,57</t>
+          <t>2,09; 12,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,35</t>
+          <t>1,51; 11,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 49,65</t>
+          <t>7,3; 50,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 50,28</t>
+          <t>16,89; 50,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 34,89</t>
+          <t>17,44; 36,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,36; 38,88</t>
+          <t>14,98; 38,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,13; 60,25</t>
+          <t>14,92; 61,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 59,2</t>
+          <t>11,16; 56,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 27,37</t>
+          <t>3,0; 27,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 37,38</t>
+          <t>4,66; 37,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,25</t>
+          <t>0,0; 37,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,57; 44,9</t>
+          <t>19,7; 46,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,56; 29,52</t>
+          <t>14,47; 29,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,59; 33,97</t>
+          <t>14,51; 33,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 44,51</t>
+          <t>11,97; 43,87</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,87; 80,27</t>
+          <t>25,06; 75,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,36; 39,04</t>
+          <t>14,09; 38,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 39,98</t>
+          <t>9,96; 43,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 42,11</t>
+          <t>11,63; 43,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,81</t>
+          <t>0,0; 44,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,58</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,84</t>
+          <t>0,0; 23,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 22,08</t>
+          <t>2,59; 21,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,76; 55,41</t>
+          <t>17,64; 54,24</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,88; 27,89</t>
+          <t>10,91; 28,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 27,95</t>
+          <t>7,99; 29,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 29,99</t>
+          <t>10,0; 29,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>42,92; 88,33</t>
+          <t>39,02; 88,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,37; 60,79</t>
+          <t>28,95; 61,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,92; 43,14</t>
+          <t>9,78; 43,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 41,5</t>
+          <t>14,73; 39,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,61</t>
+          <t>0,0; 58,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 33,04</t>
+          <t>3,16; 30,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,07; 30,73</t>
+          <t>3,89; 31,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 18,66</t>
+          <t>2,32; 19,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,2; 72,47</t>
+          <t>33,75; 72,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 39,64</t>
+          <t>17,53; 41,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 31,39</t>
+          <t>9,43; 31,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,46; 29,52</t>
+          <t>11,43; 29,56</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,53</t>
+          <t>0,0; 57,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,46; 82,28</t>
+          <t>23,66; 82,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,48</t>
+          <t>0,0; 38,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 49,19</t>
+          <t>17,13; 50,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,21</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 27,13</t>
+          <t>3,3; 26,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 26,52</t>
+          <t>8,89; 27,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,61</t>
+          <t>0,0; 31,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 24,53</t>
+          <t>5,68; 25,92</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 22,11</t>
+          <t>2,42; 21,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 33,15</t>
+          <t>15,52; 32,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,72</t>
+          <t>0,0; 26,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 9,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,89</t>
+          <t>0,0; 9,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,28</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,11; 41,52</t>
+          <t>24,54; 40,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,25; 27,12</t>
+          <t>16,98; 26,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,22; 20,48</t>
+          <t>10,34; 20,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,87; 30,55</t>
+          <t>17,21; 30,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 18,96</t>
+          <t>5,01; 18,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,26</t>
+          <t>2,57; 9,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,25; 11,95</t>
+          <t>4,14; 11,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,74</t>
+          <t>4,69; 11,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,09; 29,47</t>
+          <t>16,95; 28,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 17,44</t>
+          <t>10,96; 17,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,55</t>
+          <t>8,14; 14,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,08; 19,7</t>
+          <t>11,54; 19,11</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el trabajo en el último año</t>
+          <t>Población que ha tenido un accidente en el trabajo en el último año (tasa de respuesta: 89,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1664; 9702</t>
+          <t>1896; 9899</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1788; 9466</t>
+          <t>1798; 9515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5013</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 14622</t>
+          <t>0; 14656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1661</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3979</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5858</t>
+          <t>0; 5912</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9797</t>
+          <t>0; 10234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1958; 10680</t>
+          <t>1933; 10997</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1908; 10457</t>
+          <t>1888; 11212</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>932; 8168</t>
+          <t>923; 7032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3101; 19395</t>
+          <t>2852; 19821</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6110; 17564</t>
+          <t>5899; 17497</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14558; 28724</t>
+          <t>14355; 29676</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7813; 19771</t>
+          <t>7620; 19439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4126; 16428</t>
+          <t>4068; 16823</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2033; 10983</t>
+          <t>2071; 10390</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1154; 10408</t>
+          <t>1139; 10329</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1046; 8479</t>
+          <t>1058; 8423</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5428</t>
+          <t>0; 5602</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10467; 24018</t>
+          <t>10540; 24888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17524; 35532</t>
+          <t>17409; 35164</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10731; 24978</t>
+          <t>10671; 24707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4577; 18802</t>
+          <t>5057; 18530</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4012; 11985</t>
+          <t>3742; 11268</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8123; 22084</t>
+          <t>7972; 21751</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3638; 14337</t>
+          <t>3573; 15423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4397; 15580</t>
+          <t>4304; 15991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5743</t>
+          <t>0; 5983</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6049</t>
+          <t>0; 6087</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6723</t>
+          <t>0; 5956</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>686; 6191</t>
+          <t>727; 6025</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5034; 15706</t>
+          <t>5001; 15375</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9348; 23974</t>
+          <t>9375; 24563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4975; 17022</t>
+          <t>4864; 18047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6254; 19504</t>
+          <t>6505; 18931</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8385; 17258</t>
+          <t>7624; 17358</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10166; 22581</t>
+          <t>10754; 22673</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2571; 12439</t>
+          <t>2819; 12538</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7212; 20652</t>
+          <t>7329; 19777</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5568</t>
+          <t>0; 5668</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1083; 11574</t>
+          <t>1107; 10718</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>996; 7524</t>
+          <t>952; 7663</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>686; 5484</t>
+          <t>683; 5584</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10280; 21163</t>
+          <t>9857; 21063</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13177; 28615</t>
+          <t>12656; 29703</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4896; 16736</t>
+          <t>5030; 16798</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9069; 23364</t>
+          <t>9049; 23398</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5391</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2126; 10631</t>
+          <t>3057; 10651</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>0; 5319</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4857; 14232</t>
+          <t>4955; 14523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1686</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5515</t>
+          <t>0; 5528</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1007; 8235</t>
+          <t>1003; 8169</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3110; 9385</t>
+          <t>3146; 9879</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6467</t>
+          <t>0; 6142</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3091; 13413</t>
+          <t>3108; 14171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1050; 9803</t>
+          <t>1074; 9589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9578; 21323</t>
+          <t>9985; 21038</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1423</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1715</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3700</t>
+          <t>0; 4331</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1556</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1787</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2519</t>
+          <t>0; 3091</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1629</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 4740</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1567</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1904</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1515</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5902</t>
+          <t>0; 5391</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2463</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5885</t>
+          <t>0; 5229</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 942</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29670; 51103</t>
+          <t>30208; 50354</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>49496; 77841</t>
+          <t>48742; 76648</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20213; 40504</t>
+          <t>20451; 40329</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>33598; 60830</t>
+          <t>34267; 61139</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4963; 17783</t>
+          <t>4703; 17075</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6941; 23649</t>
+          <t>6561; 23133</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8146; 22882</t>
+          <t>7920; 21957</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10073; 25071</t>
+          <t>10027; 24561</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37066; 63918</t>
+          <t>36767; 62093</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>60244; 94567</t>
+          <t>59450; 94118</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31716; 56626</t>
+          <t>31690; 57225</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49842; 81321</t>
+          <t>47614; 78884</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15B_3_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15B_3_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 29,36</t>
+          <t>5,37; 30,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 16,21</t>
+          <t>2,8; 16,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,74</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,58</t>
+          <t>0,0; 76,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,48</t>
+          <t>0,0; 15,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>0,0; 32,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,35</t>
+          <t>0,0; 48,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,36; 24,82</t>
+          <t>4,22; 21,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 12,41</t>
+          <t>2,21; 12,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,49</t>
+          <t>1,54; 13,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 50,74</t>
+          <t>6,85; 52,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 50,08</t>
+          <t>17,17; 51,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,44; 36,05</t>
+          <t>17,33; 36,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,98; 38,22</t>
+          <t>13,48; 37,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,92; 61,7</t>
+          <t>15,02; 59,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 56,0</t>
+          <t>10,56; 54,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 27,16</t>
+          <t>3,0; 28,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 37,14</t>
+          <t>4,38; 38,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,41</t>
+          <t>0,0; 30,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 46,53</t>
+          <t>19,13; 45,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,47; 29,22</t>
+          <t>14,17; 28,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 33,6</t>
+          <t>13,75; 32,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 43,87</t>
+          <t>12,49; 42,15</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 75,47</t>
+          <t>23,12; 75,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 38,45</t>
+          <t>14,91; 38,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 43,01</t>
+          <t>10,95; 41,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 43,22</t>
+          <t>12,21; 42,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,59</t>
+          <t>0,0; 37,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 20,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,78</t>
+          <t>0,0; 22,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 21,49</t>
+          <t>2,51; 21,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 54,24</t>
+          <t>17,74; 52,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 28,58</t>
+          <t>10,72; 28,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 29,63</t>
+          <t>8,17; 29,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 29,11</t>
+          <t>10,14; 28,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,02; 88,84</t>
+          <t>42,81; 89,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,95; 61,04</t>
+          <t>29,14; 61,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 43,49</t>
+          <t>10,26; 41,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,73; 39,74</t>
+          <t>12,87; 38,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,64</t>
+          <t>0,0; 58,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 30,59</t>
+          <t>3,05; 31,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 31,29</t>
+          <t>4,01; 31,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,0</t>
+          <t>2,28; 19,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,75; 72,13</t>
+          <t>33,91; 73,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,53; 41,15</t>
+          <t>18,15; 39,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 31,51</t>
+          <t>8,47; 29,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,43; 29,56</t>
+          <t>10,89; 28,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,56</t>
+          <t>0,0; 58,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,66; 82,43</t>
+          <t>22,63; 74,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,02</t>
+          <t>0,0; 30,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 50,19</t>
+          <t>15,21; 46,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 26,91</t>
+          <t>3,22; 28,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 27,92</t>
+          <t>8,11; 26,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,92</t>
+          <t>0,0; 32,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 25,92</t>
+          <t>5,6; 23,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,62</t>
+          <t>2,38; 21,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 32,71</t>
+          <t>14,17; 31,45</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,59</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,38</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,63</t>
+          <t>0,0; 10,11</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,95</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,54; 40,91</t>
+          <t>24,28; 42,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,98; 26,71</t>
+          <t>17,04; 26,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,34; 20,39</t>
+          <t>10,14; 20,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 30,7</t>
+          <t>16,94; 30,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,2</t>
+          <t>4,76; 18,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,06</t>
+          <t>2,74; 9,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,14; 11,47</t>
+          <t>4,23; 11,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,5</t>
+          <t>4,59; 11,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,95; 28,63</t>
+          <t>17,34; 28,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,96; 17,35</t>
+          <t>11,15; 17,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 14,7</t>
+          <t>8,42; 15,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,54; 19,11</t>
+          <t>11,51; 18,72</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>9280</t>
         </is>
       </c>
     </row>
@@ -2068,22 +2068,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1896; 9899</t>
+          <t>1809; 10185</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1798; 9515</t>
+          <t>1644; 9595</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 5057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 14656</t>
+          <t>0; 15922</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,37 +2093,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4905</t>
+          <t>0; 4766</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5912</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 10234</t>
+          <t>0; 10849</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1933; 10997</t>
+          <t>1871; 9736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1888; 11212</t>
+          <t>2000; 11321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>923; 7032</t>
+          <t>944; 8033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2852; 19821</t>
+          <t>2965; 22614</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>12259</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5899; 17497</t>
+          <t>6000; 18069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14355; 29676</t>
+          <t>14264; 30278</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7620; 19439</t>
+          <t>6855; 19012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4068; 16823</t>
+          <t>4986; 19781</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2071; 10390</t>
+          <t>1960; 10035</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1139; 10329</t>
+          <t>1139; 10744</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1058; 8423</t>
+          <t>994; 8755</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5602</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10540; 24888</t>
+          <t>10230; 24518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17409; 35164</t>
+          <t>17049; 34881</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10671; 24707</t>
+          <t>10113; 24120</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5057; 18530</t>
+          <t>6061; 20455</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11819</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3742; 11268</t>
+          <t>3451; 11341</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7972; 21751</t>
+          <t>8432; 21608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3573; 15423</t>
+          <t>3925; 14913</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4304; 15991</t>
+          <t>4708; 16455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5983</t>
+          <t>0; 5012</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6087</t>
+          <t>0; 6077</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5956</t>
+          <t>0; 5736</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>727; 6025</t>
+          <t>765; 6446</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5001; 15375</t>
+          <t>5028; 14910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9375; 24563</t>
+          <t>9210; 24722</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4864; 18047</t>
+          <t>4979; 17864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6505; 18931</t>
+          <t>6998; 19912</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>16033</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7624; 17358</t>
+          <t>8363; 17432</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10754; 22673</t>
+          <t>10824; 22680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2819; 12538</t>
+          <t>2958; 12041</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7329; 19777</t>
+          <t>7054; 20931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5668</t>
+          <t>0; 5624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1107; 10718</t>
+          <t>1068; 11105</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>952; 7663</t>
+          <t>981; 7658</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>683; 5584</t>
+          <t>745; 6439</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9857; 21063</t>
+          <t>9903; 21475</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12656; 29703</t>
+          <t>13099; 28565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5030; 16798</t>
+          <t>4516; 15971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9049; 23398</t>
+          <t>9518; 24841</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6144</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>15285</t>
         </is>
       </c>
     </row>
@@ -2900,22 +2900,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5393</t>
+          <t>0; 5474</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3057; 10651</t>
+          <t>2924; 9636</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5319</t>
+          <t>0; 4228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4955; 14523</t>
+          <t>4790; 14661</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,37 +2925,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5528</t>
+          <t>0; 4474</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1003; 8169</t>
+          <t>977; 8728</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3146; 9879</t>
+          <t>3108; 10311</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6142</t>
+          <t>0; 6209</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3108; 14171</t>
+          <t>3060; 13097</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1074; 9589</t>
+          <t>1058; 9733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9985; 21038</t>
+          <t>9889; 21950</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t>479</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1401</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4331</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3091</t>
+          <t>0; 2621</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4740</t>
+          <t>0; 5495</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5391</t>
+          <t>0; 5879</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5229</t>
+          <t>0; 6658</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46487</t>
+          <t>49506</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>62259</t>
+          <t>66076</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30208; 50354</t>
+          <t>29880; 51811</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48742; 76648</t>
+          <t>48908; 76630</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20451; 40329</t>
+          <t>20044; 40235</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>34267; 61139</t>
+          <t>37246; 66343</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4703; 17075</t>
+          <t>4464; 16998</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6561; 23133</t>
+          <t>7005; 23025</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7920; 21957</t>
+          <t>8102; 22800</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10027; 24561</t>
+          <t>10660; 26274</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>36767; 62093</t>
+          <t>37616; 62717</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>59450; 94118</t>
+          <t>60449; 92848</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>31690; 57225</t>
+          <t>32791; 58691</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>47614; 78884</t>
+          <t>52043; 84630</t>
         </is>
       </c>
     </row>
